--- a/docs/all/idx14_seguridad_loadings_y_tops.xlsx
+++ b/docs/all/idx14_seguridad_loadings_y_tops.xlsx
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.6105029148964697</v>
+        <v>0.61050291489647</v>
       </c>
       <c r="D2">
-        <v>0.3310333456742149</v>
+        <v>0.331033345674215</v>
       </c>
       <c r="E2">
         <v>33.1</v>
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.6281153860962065</v>
+        <v>0.6281153860962062</v>
       </c>
       <c r="D3">
-        <v>0.3405833660337874</v>
+        <v>0.3405833660337871</v>
       </c>
       <c r="E3">
         <v>34.1</v>
@@ -438,10 +438,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.4732877519263806</v>
+        <v>0.4732877519263804</v>
       </c>
       <c r="D4">
-        <v>0.256631089162591</v>
+        <v>0.2566310891625908</v>
       </c>
       <c r="E4">
         <v>25.7</v>
@@ -459,10 +459,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.0667243924681265</v>
+        <v>-0.06672439246812695</v>
       </c>
       <c r="D5">
-        <v>0.03618000559513959</v>
+        <v>0.03618000559513982</v>
       </c>
       <c r="E5">
         <v>3.6</v>
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.06560344486656025</v>
+        <v>-0.06560344486656081</v>
       </c>
       <c r="D6">
-        <v>0.03557219353426697</v>
+        <v>0.03557219353426726</v>
       </c>
       <c r="E6">
         <v>3.6</v>
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.05823388518792889</v>
+        <v>0.05823388518792903</v>
       </c>
       <c r="D7">
-        <v>0.03137076480500093</v>
+        <v>0.03137076480500101</v>
       </c>
       <c r="E7">
         <v>3.1</v>
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.1346209372819188</v>
+        <v>0.1346209372819184</v>
       </c>
       <c r="D8">
-        <v>0.07252069388245556</v>
+        <v>0.07252069388245538</v>
       </c>
       <c r="E8">
         <v>7.3</v>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>-0.4269360511709004</v>
+        <v>-0.4269360511709012</v>
       </c>
       <c r="D9">
-        <v>0.2299917033671388</v>
+        <v>0.2299917033671393</v>
       </c>
       <c r="E9">
         <v>23</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.7441984355463245</v>
+        <v>-0.744198435546324</v>
       </c>
       <c r="D10">
-        <v>0.4009018806564656</v>
+        <v>0.4009018806564654</v>
       </c>
       <c r="E10">
         <v>40.1</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C11">
-        <v>-0.4923213529822354</v>
+        <v>-0.4923213529822348</v>
       </c>
       <c r="D11">
-        <v>0.2652149572889392</v>
+        <v>0.2652149572889389</v>
       </c>
       <c r="E11">
         <v>26.5</v>
@@ -606,10 +606,10 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.2234835357802962</v>
+        <v>-0.2234835357802967</v>
       </c>
       <c r="D12">
-        <v>0.1291288646821641</v>
+        <v>0.1291288646821644</v>
       </c>
       <c r="E12">
         <v>12.9</v>
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.02427606128192768</v>
+        <v>0.02427606128192742</v>
       </c>
       <c r="D13">
-        <v>0.01402671664981928</v>
+        <v>0.01402671664981912</v>
       </c>
       <c r="E13">
         <v>1.4</v>
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.1995633361688084</v>
+        <v>0.1995633361688091</v>
       </c>
       <c r="D14">
-        <v>0.115307765029263</v>
+        <v>0.1153077650292634</v>
       </c>
       <c r="E14">
         <v>11.5</v>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="C15">
-        <v>0.4341925678421927</v>
+        <v>0.4341925678421917</v>
       </c>
       <c r="D15">
-        <v>0.2508766166739657</v>
+        <v>0.250876616673965</v>
       </c>
       <c r="E15">
         <v>25.1</v>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.84918612269134</v>
+        <v>-0.8491861226913402</v>
       </c>
       <c r="D16">
-        <v>0.4906600369647879</v>
+        <v>0.490660036964788</v>
       </c>
       <c r="E16">
         <v>49.1</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C17">
-        <v>-0.3747888635341829</v>
+        <v>-0.3747888635341826</v>
       </c>
       <c r="D17">
-        <v>0.2003927729015442</v>
+        <v>0.2003927729015439</v>
       </c>
       <c r="E17">
         <v>20</v>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C18">
-        <v>-0.2452270562690024</v>
+        <v>-0.2452270562690027</v>
       </c>
       <c r="D18">
-        <v>0.1311184364786932</v>
+        <v>0.1311184364786933</v>
       </c>
       <c r="E18">
         <v>13.1</v>
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C19">
-        <v>0.7390977179475873</v>
+        <v>0.7390977179475867</v>
       </c>
       <c r="D19">
-        <v>0.3951820759775908</v>
+        <v>0.3951820759775903</v>
       </c>
       <c r="E19">
         <v>39.5</v>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="C20">
-        <v>-0.5030565909225071</v>
+        <v>-0.5030565909225082</v>
       </c>
       <c r="D20">
-        <v>0.268975188405417</v>
+        <v>0.2689751884054174</v>
       </c>
       <c r="E20">
         <v>26.9</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.008101129457594993</v>
+        <v>0.008101129457595639</v>
       </c>
       <c r="D21">
-        <v>0.004331526236754841</v>
+        <v>0.004331526236755184</v>
       </c>
       <c r="E21">
         <v>0.4</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.6583945796592841</v>
+        <v>0.6583945796592839</v>
       </c>
       <c r="D22">
-        <v>0.3961467088380323</v>
+        <v>0.3961467088380324</v>
       </c>
       <c r="E22">
         <v>39.6</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>-0.72568769365122</v>
+        <v>-0.7256876936512201</v>
       </c>
       <c r="D23">
-        <v>0.4366360239978918</v>
+        <v>0.4366360239978921</v>
       </c>
       <c r="E23">
         <v>43.7</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.0873690464003988</v>
+        <v>0.08736904640039828</v>
       </c>
       <c r="D24">
-        <v>0.0525687198150178</v>
+        <v>0.0525687198150175</v>
       </c>
       <c r="E24">
         <v>5.3</v>
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.01128823902080942</v>
+        <v>-0.01128823902080918</v>
       </c>
       <c r="D25">
-        <v>0.006791973802373702</v>
+        <v>0.006791973802373563</v>
       </c>
       <c r="E25">
         <v>0.7</v>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C26">
-        <v>-0.1792572847873737</v>
+        <v>-0.1792572847873736</v>
       </c>
       <c r="D26">
         <v>0.1078565735466844</v>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.2386885500666323</v>
+        <v>0.2386885500666321</v>
       </c>
     </row>
     <row r="4">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.1913705960963166</v>
+        <v>0.1913705960963165</v>
       </c>
     </row>
     <row r="5">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.1187902613969193</v>
+        <v>0.1187902613969194</v>
       </c>
     </row>
     <row r="6">
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.07892840216104643</v>
+        <v>0.07892840216104641</v>
       </c>
     </row>
   </sheetData>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.6281153860962065</v>
+        <v>0.6281153860962062</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.6105029148964697</v>
+        <v>0.61050291489647</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.4732877519263806</v>
+        <v>0.4732877519263804</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.0667243924681265</v>
+        <v>-0.06672439246812695</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.06560344486656025</v>
+        <v>-0.06560344486656081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.7441984355463245</v>
+        <v>-0.744198435546324</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.4923213529822354</v>
+        <v>-0.4923213529822348</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.4269360511709004</v>
+        <v>-0.4269360511709012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.1346209372819188</v>
+        <v>0.1346209372819184</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.05823388518792889</v>
+        <v>0.05823388518792903</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
